--- a/Tests/Test Config From EXCEL/testdata/getattributeasdbl3.xlsx
+++ b/Tests/Test Config From EXCEL/testdata/getattributeasdbl3.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="attributes" sheetId="1" r:id="R31205d83af5e459d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="attributes" sheetId="1" r:id="R76a614b306da4e68"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -72,7 +72,7 @@
     </x:row>
   </x:sheetData>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d663752796b4804"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R59e4816ba4ab42f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>